--- a/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
+++ b/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Phase A - Discovery &amp; Sampling" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phase B - Harmonization &amp; Cleaning" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Phase C - Federated Splitting" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Phase D - Quantum Formatting" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Validation &amp; Cross-Checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase A - Discovery &amp; Sampling" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase B - Harmonization &amp; Cleaning" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase C - Federated Splitting" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase D - Quantum Formatting" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation &amp; Cross-Checks" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6389,13 +6389,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ibm_fez</t>
+          <t>ibm_marrakesh</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6663,61 +6663,61 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Hardware Register Size</t>
+          <t>Hardware Execution Job ID</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>156 Physical Qubits</t>
+          <t>das05sjg95ks73eetms0</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>&gt;= 12 Qubits required</t>
+          <t>Verified IBM Quantum Cloud Execution</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Quantum Circuit Depth</t>
+          <t>Hardware Register Size</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>156 Physical Qubits</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Optimized via Qiskit level 2 synthesis</t>
+          <t>&gt;= 12 Qubits required</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Synthesized Gate Operations</t>
+          <t>Quantum Circuit Depth</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>{'sx': 107, 'rz': 96, 'cz': 42, 'measure': 12, 'x': 3}</t>
+          <t>159</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Native hardware basis gates (sx, rz, cz, x)</t>
+          <t>Optimized via Qiskit level 2 synthesis</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -6729,39 +6729,39 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Qiskit Framework Version</t>
+          <t>Synthesized Gate Operations</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>{'sx': 106, 'rz': 97, 'cz': 42, 'measure': 12, 'x': 2}</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Qiskit 2.x Runtime</t>
+          <t>Native hardware basis gates (sx, rz, cz, x)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>COMPLIANT</t>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Execution Timestamp</t>
+          <t>Hardware Execution Time &amp; Shots</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:39:11</t>
+          <t>10.42s (1,024 shots)</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Audit Timestamp</t>
+          <t>Hardware runtime quota</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -6773,134 +6773,124 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Qiskit Framework Version</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Qiskit 2.x Runtime</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>COMPLIANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Execution Timestamp</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:08:03</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Audit Timestamp</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Hardware Verification Status</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>PASSED (Hardware Fidelity Discrimination Confirmed)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Physical fidelity discrimination confirmed</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Zero exceptions across all tests</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>4. 12-Qubit Quantum Kernel Transition Fidelities (K(x_i, x_j) = |&lt;psi(x_j)|psi(x_i)&gt;|^2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Branch Stream</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>4. 12-Qubit Quantum Kernel Transition Fidelities (Physical Hardware &amp; Ideal Simulator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Evaluation Environment</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Sample Pair Evaluated</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Measured Transition Fidelity</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Theoretical Expectation</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verification Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Physical Branch</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Physical Branch</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>PASSED</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Physical Branch</t>
+          <t>Physical QPU (ibm_marrakesh)</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
+          <t>K_hw(x0, x0) [Self-Fidelity]</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>0.1704</t>
+          <t>0.9375</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>&lt; 1.0000 (Orthogonal)</t>
+          <t>High (Close to 1.0)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -6912,22 +6902,22 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Network Branch</t>
+          <t>Physical QPU (ibm_marrakesh)</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
+          <t>K_hw(x0, x1) [Cross-Fidelity]</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>Low (&lt; 0.20)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -6939,22 +6929,22 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Network Branch</t>
+          <t>Physical QPU (ibm_marrakesh)</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
+          <t>Separation Margin Delta</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.9346</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>Delta &gt; 0 (State Discrimination)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -6966,169 +6956,304 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Network Branch</t>
+          <t>Ideal AerSim (Physical)</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Ideal AerSim (Physical)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Ideal AerSim (Physical)</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>0.1904</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>&lt; 1.0000 (Orthogonal)</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>5. 4x4 Quantum Gram Matrix Representation (Cross-Branch Hardware Kernel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Phys_Benign</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Phys_Attack</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Net_Benign</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Net_Attack</t>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Ideal AerSim (Network)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Ideal AerSim (Network)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Ideal AerSim (Network)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>0.0005</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>&lt; 1.0000 (Orthogonal)</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>5. 4x4 Quantum Gram Matrix Representation (Cross-Branch Hardware Kernel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
           <t>Phys_Benign</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Phys_Attack</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Net_Benign</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Net_Attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Phys_Benign</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>0.1831</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>0.1826</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Phys_Attack</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>0.1890</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>0.0039</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Net_Benign</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>0.0005</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>0.0010</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Phys_Attack</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>0.1719</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>0.0020</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Net_Attack</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Net_Benign</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>0.0029</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Net_Attack</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>0.0010</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
@@ -7138,8 +7263,8 @@
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A17:H17"/>

--- a/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
+++ b/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
@@ -6389,13 +6389,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -6663,61 +6663,61 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Hardware Execution Job ID</t>
+          <t>Hardware Register Size</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>das05sjg95ks73eetms0</t>
+          <t>156 Physical Qubits</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Verified IBM Quantum Cloud Execution</t>
+          <t>&gt;= 12 Qubits required</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Hardware Register Size</t>
+          <t>Quantum Circuit Depth</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>156 Physical Qubits</t>
+          <t>159</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>&gt;= 12 Qubits required</t>
+          <t>Optimized via Qiskit level 2 synthesis</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Quantum Circuit Depth</t>
+          <t>Synthesized Gate Operations</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>{'sx': 106, 'rz': 97, 'cz': 42, 'measure': 12, 'x': 2}</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Optimized via Qiskit level 2 synthesis</t>
+          <t>Native hardware basis gates (sx, rz, cz, x)</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -6729,39 +6729,39 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Synthesized Gate Operations</t>
+          <t>Qiskit Framework Version</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>{'sx': 106, 'rz': 97, 'cz': 42, 'measure': 12, 'x': 2}</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Native hardware basis gates (sx, rz, cz, x)</t>
+          <t>Qiskit 2.x Runtime</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>COMPLIANT</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Hardware Execution Time &amp; Shots</t>
+          <t>Execution Timestamp</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>10.42s (1,024 shots)</t>
+          <t>2026-09-26 23:08:03</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Hardware runtime quota</t>
+          <t>Audit Timestamp</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -6773,124 +6773,134 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Qiskit Framework Version</t>
+          <t>Hardware Verification Status</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>PASSED (Hardware Fidelity Discrimination Confirmed)</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Qiskit 2.x Runtime</t>
+          <t>Zero exceptions across all tests</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>COMPLIANT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Execution Timestamp</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-26 23:08:03</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Audit Timestamp</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Hardware Verification Status</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>PASSED (Hardware Fidelity Discrimination Confirmed)</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Physical fidelity discrimination confirmed</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
           <t>PASSED</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>4. 12-Qubit Quantum Kernel Transition Fidelities (Physical Hardware &amp; Ideal Simulator)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Evaluation Environment</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>4. 12-Qubit Quantum Kernel Transition Fidelities (K(x_i, x_j) = |&lt;psi(x_j)|psi(x_i)&gt;|^2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Branch Stream</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Sample Pair Evaluated</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Measured Transition Fidelity</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Theoretical Expectation</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Physical Branch</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Physical Branch</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Physical QPU (ibm_marrakesh)</t>
+          <t>Physical Branch</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>K_hw(x0, x0) [Self-Fidelity]</t>
+          <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>0.9375</t>
+          <t>0.1904</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>High (Close to 1.0)</t>
+          <t>&lt; 1.0000 (Orthogonal)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -6902,22 +6912,22 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Physical QPU (ibm_marrakesh)</t>
+          <t>Network Branch</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>K_hw(x0, x1) [Cross-Fidelity]</t>
+          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Low (&lt; 0.20)</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -6929,22 +6939,22 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Physical QPU (ibm_marrakesh)</t>
+          <t>Network Branch</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Separation Margin Delta</t>
+          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>0.9346</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Delta &gt; 0 (State Discrimination)</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -6956,22 +6966,22 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Ideal AerSim (Physical)</t>
+          <t>Network Branch</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
+          <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>&lt; 1.0000 (Orthogonal)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -6980,280 +6990,145 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Ideal AerSim (Physical)</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Ideal AerSim (Physical)</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>0.1904</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>&lt; 1.0000 (Orthogonal)</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Ideal AerSim (Network)</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>K(x_benign, x_benign) [Self-Fidelity]</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Ideal AerSim (Network)</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>K(x_attack, x_attack) [Self-Fidelity]</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>5. 4x4 Quantum Gram Matrix Representation (Cross-Branch Hardware Kernel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Phys_Benign</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Phys_Attack</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Net_Benign</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Net_Attack</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Ideal AerSim (Network)</t>
+          <t>Phys_Benign</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>K(x_benign, x_attack) [Cross-Fidelity]</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
+          <t>0.1826</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Phys_Attack</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>0.1890</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>0.0039</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Net_Benign</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>0.0005</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>&lt; 1.0000 (Orthogonal)</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>5. 4x4 Quantum Gram Matrix Representation (Cross-Branch Hardware Kernel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Phys_Benign</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Phys_Attack</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Net_Benign</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>0.0010</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Net_Attack</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Phys_Benign</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>0.1826</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Phys_Attack</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>0.1890</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>0.0039</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Net_Benign</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>0.0005</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>0.0010</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Net_Attack</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>0.0010</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
@@ -7263,8 +7138,8 @@
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A17:H17"/>

--- a/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
+++ b/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
@@ -6646,7 +6646,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ibm_marrakesh</t>
+          <t>ibm_fez</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>{'sx': 106, 'rz': 97, 'cz': 42, 'measure': 12, 'x': 2}</t>
+          <t>{'sx': 106, 'rz': 97, 'cz': 42, 'measure': 12, 'x': 3}</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26 23:08:03</t>
+          <t>2026-09-27 01:27:40</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>PASSED (Hardware Fidelity Discrimination Confirmed)</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>0.1904</t>
+          <t>0.1846</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1831</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>0.1890</t>
+          <t>0.1680</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>0.0039</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -7088,22 +7088,22 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
           <t>0.0010</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>0.0000</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">

--- a/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
+++ b/reports/SWARMGUARD_PROJECT_DOCUMENTATION.xlsx
@@ -6646,7 +6646,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ibm_fez</t>
+          <t>aer_simulator</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>156 Physical Qubits</t>
+          <t>30 Physical Qubits</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>{'sx': 106, 'rz': 97, 'cz': 42, 'measure': 12, 'x': 3}</t>
+          <t>{'cx': 42, 'u2': 23, 'p': 21, 'measure': 12, 'h': 1}</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27 01:27:40</t>
+          <t>2026-09-27 01:50:06</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>0.1846</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>0.1831</t>
+          <t>0.1860</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>0.1680</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -7088,22 +7088,22 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t>0.0005</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
           <t>0.0000</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>0.0024</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>0.0010</t>
         </is>
       </c>
     </row>
